--- a/H5509_V2/bin/Debug/Logs/202510/Log_20251031-170623.xlsx
+++ b/H5509_V2/bin/Debug/Logs/202510/Log_20251031-170623.xlsx
@@ -932,6 +932,36 @@
   </x:si>
   <x:si>
     <x:t>PS抓盘手臂放空盘到Auto2流程.Processing=False;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-10-31 21:02:52]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 HardwareGXN.GSNAxisController.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 149
+   在 HardwareGXN.GSNAxisController.InitCard() 位置 D:\GitHub\H5509_V2\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-10-31 21:14:06]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 HardwareGXN.GSNAxisController.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 149
+   在 HardwareGXN.GSNAxisController.InitCard() 位置 D:\GitHub\H5509_V2\HardwareGXN\GSNAxisCard\GSNAxisController.cs:行号 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：SELECT * FROM dut_3232323_20251029_18_59_23，错误信息：对象名 'dut_3232323_20251029_18_59_23' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>输入字符串的格式不正确。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_3232323_20251029_18_59_23 where 名称='auto1'，错误信息：对象名 'o_3232323_20251029_18_59_23' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select * from f_3232323_20251029_18_59_23  order by 获取MAP时间，错误信息：对象名 'f_3232323_20251029_18_59_23' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>密码错误！</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[CEHSE_BGA153_11.5X13_8X19_UBOT_SMI2730_FT3]:测试机名称:[CEHSE_BGA153_11.5X13_8X19_UBOT_SMI2730_FT3]:[Dout连续不良自动关闭]:False-&gt;True:更新成功</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5496,6 +5526,370 @@
         <x:v>304</x:v>
       </x:c>
     </x:row>
+    <x:row r="301" spans="1:4">
+      <x:c r="A301" s="1">
+        <x:v>45961.8769893519</x:v>
+      </x:c>
+      <x:c r="B301" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C301" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D301" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:4">
+      <x:c r="A302" s="1">
+        <x:v>45961.8769919329</x:v>
+      </x:c>
+      <x:c r="B302" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C302" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D302" s="2" t="s">
+        <x:v>305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:4">
+      <x:c r="A303" s="1">
+        <x:v>45961.8771222569</x:v>
+      </x:c>
+      <x:c r="B303" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C303" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D303" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:4">
+      <x:c r="A304" s="1">
+        <x:v>45961.8847911458</x:v>
+      </x:c>
+      <x:c r="B304" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C304" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D304" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:4">
+      <x:c r="A305" s="1">
+        <x:v>45961.8847922685</x:v>
+      </x:c>
+      <x:c r="B305" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C305" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D305" s="2" t="s">
+        <x:v>306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:4">
+      <x:c r="A306" s="1">
+        <x:v>45961.8848972338</x:v>
+      </x:c>
+      <x:c r="B306" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C306" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D306" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:4">
+      <x:c r="A307" s="1">
+        <x:v>45961.8849112963</x:v>
+      </x:c>
+      <x:c r="B307" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C307" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D307" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:4">
+      <x:c r="A308" s="1">
+        <x:v>45961.8849185069</x:v>
+      </x:c>
+      <x:c r="B308" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C308" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D308" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:4">
+      <x:c r="A309" s="1">
+        <x:v>45961.8849590162</x:v>
+      </x:c>
+      <x:c r="B309" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C309" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D309" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:4">
+      <x:c r="A310" s="1">
+        <x:v>45961.8849597454</x:v>
+      </x:c>
+      <x:c r="B310" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C310" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D310" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" spans="1:4">
+      <x:c r="A311" s="1">
+        <x:v>45961.8849715972</x:v>
+      </x:c>
+      <x:c r="B311" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C311" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D311" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:4">
+      <x:c r="A312" s="1">
+        <x:v>45961.8849761458</x:v>
+      </x:c>
+      <x:c r="B312" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C312" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D312" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:4">
+      <x:c r="A313" s="1">
+        <x:v>45961.8850083912</x:v>
+      </x:c>
+      <x:c r="B313" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C313" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D313" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:4">
+      <x:c r="A314" s="1">
+        <x:v>45961.8850220718</x:v>
+      </x:c>
+      <x:c r="B314" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C314" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D314" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:4">
+      <x:c r="A315" s="1">
+        <x:v>45961.8850275347</x:v>
+      </x:c>
+      <x:c r="B315" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C315" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D315" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:4">
+      <x:c r="A316" s="1">
+        <x:v>45961.8850315394</x:v>
+      </x:c>
+      <x:c r="B316" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C316" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D316" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:4">
+      <x:c r="A317" s="1">
+        <x:v>45961.8850353704</x:v>
+      </x:c>
+      <x:c r="B317" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C317" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D317" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:4">
+      <x:c r="A318" s="1">
+        <x:v>45961.8850388426</x:v>
+      </x:c>
+      <x:c r="B318" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C318" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D318" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:4">
+      <x:c r="A319" s="1">
+        <x:v>45961.8850417477</x:v>
+      </x:c>
+      <x:c r="B319" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C319" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D319" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:4">
+      <x:c r="A320" s="1">
+        <x:v>45961.8850883333</x:v>
+      </x:c>
+      <x:c r="B320" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C320" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D320" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:4">
+      <x:c r="A321" s="1">
+        <x:v>45961.885094537</x:v>
+      </x:c>
+      <x:c r="B321" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C321" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D321" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:4">
+      <x:c r="A322" s="1">
+        <x:v>45961.8851770486</x:v>
+      </x:c>
+      <x:c r="B322" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C322" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D322" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:4">
+      <x:c r="A323" s="1">
+        <x:v>45961.8851872454</x:v>
+      </x:c>
+      <x:c r="B323" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C323" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D323" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:4">
+      <x:c r="A324" s="1">
+        <x:v>45961.8852183796</x:v>
+      </x:c>
+      <x:c r="B324" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C324" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D324" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:4">
+      <x:c r="A325" s="1">
+        <x:v>45961.8856248843</x:v>
+      </x:c>
+      <x:c r="B325" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C325" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D325" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:4">
+      <x:c r="A326" s="1">
+        <x:v>45961.8863045833</x:v>
+      </x:c>
+      <x:c r="B326" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C326" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D326" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
